--- a/erp-server/erp-server-scm/src/main/resources/excel/purchaseContractExport.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchaseContractExport.xlsx
@@ -4,18 +4,31 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28125" windowHeight="12540"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
   <si>
     <t>进货订单</t>
   </si>
@@ -62,70 +75,97 @@
     <t>数量</t>
   </si>
   <si>
+    <t>未税单价</t>
+  </si>
+  <si>
+    <t>未税金额</t>
+  </si>
+  <si>
+    <t>税率</t>
+  </si>
+  <si>
+    <t>含税单价</t>
+  </si>
+  <si>
+    <t>含税金额</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>{.sort}</t>
+  </si>
+  <si>
+    <t>{.img}</t>
+  </si>
+  <si>
+    <t>{.skuNo}</t>
+  </si>
+  <si>
+    <t>{.productName}</t>
+  </si>
+  <si>
+    <t>{.unit}</t>
+  </si>
+  <si>
+    <t>{.qty}</t>
+  </si>
+  <si>
+    <t>{.price}</t>
+  </si>
+  <si>
+    <t>{.amount}</t>
+  </si>
+  <si>
+    <t>{.taxRate}</t>
+  </si>
+  <si>
+    <t>{.taxPrice}</t>
+  </si>
+  <si>
+    <t>{.taxAmount}</t>
+  </si>
+  <si>
+    <t>{.remark}</t>
+  </si>
+  <si>
+    <t>制单人：</t>
+  </si>
+  <si>
+    <t>{createUserName}</t>
+  </si>
+  <si>
+    <t>合计数量：</t>
+  </si>
+  <si>
+    <t>{sumQty}</t>
+  </si>
+  <si>
+    <t>合计金额：</t>
+  </si>
+  <si>
+    <t>{sumAmount}</t>
+  </si>
+  <si>
+    <t>{sumTaxAmount}</t>
+  </si>
+  <si>
+    <t>采购主管：</t>
+  </si>
+  <si>
+    <t>{approveUserName}</t>
+  </si>
+  <si>
     <t>单价</t>
   </si>
   <si>
     <t>金额</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>{.sort}</t>
-  </si>
-  <si>
-    <t>{.img}</t>
-  </si>
-  <si>
-    <t>{.skuNo}</t>
-  </si>
-  <si>
-    <t>{.productName}</t>
-  </si>
-  <si>
-    <t>{.unit}</t>
-  </si>
-  <si>
-    <t>{.qty}</t>
-  </si>
-  <si>
-    <t>{.price}</t>
-  </si>
-  <si>
-    <t>{.amount}</t>
-  </si>
-  <si>
-    <t>{.remark}</t>
-  </si>
-  <si>
-    <t>制单人：</t>
-  </si>
-  <si>
-    <t>{createUserName}</t>
-  </si>
-  <si>
-    <t>合计数量：</t>
-  </si>
-  <si>
-    <t>{sumQty}</t>
-  </si>
-  <si>
-    <t>合计金额：</t>
-  </si>
-  <si>
-    <t>{sumAmount}</t>
-  </si>
-  <si>
-    <t>采购主管：</t>
-  </si>
-  <si>
-    <t>{approveUserName}</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -173,27 +213,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -210,6 +229,45 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color theme="3"/>
@@ -219,39 +277,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -304,7 +330,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -319,49 +359,133 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -373,121 +497,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -524,21 +564,6 @@
       </top>
       <bottom style="thin">
         <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -572,6 +597,21 @@
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -628,148 +668,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -847,52 +887,52 @@
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="货币[0]" xfId="1" builtinId="7"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="2" builtinId="38"/>
-    <cellStyle name="输入" xfId="3" builtinId="20"/>
-    <cellStyle name="货币" xfId="4" builtinId="4"/>
-    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="6" builtinId="39"/>
-    <cellStyle name="差" xfId="7" builtinId="27"/>
-    <cellStyle name="千位分隔" xfId="8" builtinId="3"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="9" builtinId="40"/>
-    <cellStyle name="超链接" xfId="10" builtinId="8"/>
-    <cellStyle name="百分比" xfId="11" builtinId="5"/>
-    <cellStyle name="已访问的超链接" xfId="12" builtinId="9"/>
-    <cellStyle name="注释" xfId="13" builtinId="10"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="14" builtinId="36"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
     <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="警告文本" xfId="16" builtinId="11"/>
-    <cellStyle name="标题" xfId="17" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="18" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="19" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="20" builtinId="17"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="21" builtinId="32"/>
-    <cellStyle name="标题 3" xfId="22" builtinId="18"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="23" builtinId="44"/>
-    <cellStyle name="输出" xfId="24" builtinId="21"/>
-    <cellStyle name="计算" xfId="25" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="26" builtinId="23"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="27" builtinId="50"/>
-    <cellStyle name="强调文字颜色 2" xfId="28" builtinId="33"/>
-    <cellStyle name="链接单元格" xfId="29" builtinId="24"/>
-    <cellStyle name="汇总" xfId="30" builtinId="25"/>
-    <cellStyle name="好" xfId="31" builtinId="26"/>
-    <cellStyle name="适中" xfId="32" builtinId="28"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="33" builtinId="46"/>
-    <cellStyle name="强调文字颜色 1" xfId="34" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="35" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="36" builtinId="31"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="37" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="38" builtinId="35"/>
-    <cellStyle name="强调文字颜色 3" xfId="39" builtinId="37"/>
-    <cellStyle name="强调文字颜色 4" xfId="40" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="41" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="42" builtinId="43"/>
-    <cellStyle name="强调文字颜色 5" xfId="43" builtinId="45"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="45" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
@@ -1168,7 +1208,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:P27"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="7.42857142857143" style="14" customWidth="1"/>
@@ -1176,14 +1216,14 @@
     <col min="3" max="3" width="16.7142857142857" style="14" customWidth="1"/>
     <col min="4" max="4" width="19.2857142857143" style="14" customWidth="1"/>
     <col min="5" max="5" width="8.00952380952381" style="14"/>
-    <col min="6" max="6" width="10.4285714285714" style="14" customWidth="1"/>
-    <col min="7" max="7" width="11.1428571428571" style="14" customWidth="1"/>
-    <col min="8" max="8" width="12.5714285714286" style="14" customWidth="1"/>
-    <col min="9" max="9" width="16.8571428571429" style="14" customWidth="1"/>
-    <col min="10" max="16384" width="10.2857142857143" style="14"/>
+    <col min="6" max="8" width="10.4285714285714" style="14" customWidth="1"/>
+    <col min="9" max="10" width="11.1428571428571" style="14" customWidth="1"/>
+    <col min="11" max="11" width="12.5714285714286" style="14" customWidth="1"/>
+    <col min="12" max="12" width="16.8571428571429" style="14" customWidth="1"/>
+    <col min="13" max="16384" width="10.2857142857143" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" ht="0.75" customHeight="1" spans="1:9">
+    <row r="1" ht="0.75" customHeight="1" spans="1:12">
       <c r="A1" s="15"/>
       <c r="B1" s="15"/>
       <c r="C1" s="15"/>
@@ -1193,8 +1233,11 @@
       <c r="G1" s="15"/>
       <c r="H1" s="15"/>
       <c r="I1" s="15"/>
-    </row>
-    <row r="2" ht="23.4" customHeight="1" spans="1:13">
+      <c r="J1" s="15"/>
+      <c r="K1" s="15"/>
+      <c r="L1" s="15"/>
+    </row>
+    <row r="2" ht="23.4" customHeight="1" spans="1:16">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1206,11 +1249,14 @@
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
       <c r="I2" s="1"/>
-      <c r="K2" s="20"/>
-      <c r="L2" s="20"/>
-      <c r="M2" s="20"/>
-    </row>
-    <row r="3" ht="22.65" customHeight="1" spans="1:13">
+      <c r="J2" s="1"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+      <c r="N2" s="20"/>
+      <c r="O2" s="20"/>
+      <c r="P2" s="20"/>
+    </row>
+    <row r="3" ht="22.65" customHeight="1" spans="1:16">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1225,18 +1271,21 @@
         <v>4</v>
       </c>
       <c r="F3" s="3"/>
-      <c r="G3" s="2" t="s">
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
+      <c r="I3" s="2"/>
+      <c r="J3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="K3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="I3" s="4"/>
-      <c r="K3" s="21"/>
-      <c r="L3" s="20"/>
-      <c r="M3" s="21"/>
-    </row>
-    <row r="4" ht="20.4" customHeight="1" spans="1:13">
+      <c r="L3" s="4"/>
+      <c r="N3" s="21"/>
+      <c r="O3" s="20"/>
+      <c r="P3" s="21"/>
+    </row>
+    <row r="4" ht="20.4" customHeight="1" spans="1:16">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1250,11 +1299,14 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
-      <c r="K4" s="21"/>
-      <c r="L4" s="21"/>
-      <c r="M4" s="21"/>
-    </row>
-    <row r="5" s="13" customFormat="1" ht="22" customHeight="1" spans="1:13">
+      <c r="J4" s="5"/>
+      <c r="K4" s="5"/>
+      <c r="L4" s="5"/>
+      <c r="N4" s="21"/>
+      <c r="O4" s="21"/>
+      <c r="P4" s="21"/>
+    </row>
+    <row r="5" s="13" customFormat="1" ht="22" customHeight="1" spans="1:16">
       <c r="A5" s="16" t="s">
         <v>9</v>
       </c>
@@ -1282,69 +1334,94 @@
       <c r="I5" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="21"/>
-    </row>
-    <row r="6" ht="19" customHeight="1" spans="1:9">
+      <c r="J5" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="21"/>
+    </row>
+    <row r="6" ht="19" customHeight="1" spans="1:12">
       <c r="A6" s="16" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G6" s="16" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H6" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" ht="23" customHeight="1" spans="1:9">
+        <v>28</v>
+      </c>
+      <c r="I6" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="J6" s="16" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" ht="23" customHeight="1" spans="1:12">
       <c r="A7" s="9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E7" s="12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F7" s="12"/>
       <c r="G7" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H7" s="12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I7" s="12"/>
-    </row>
-    <row r="8" ht="21" customHeight="1" spans="1:9">
+      <c r="J7" s="9" t="s">
+        <v>37</v>
+      </c>
+      <c r="K7" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="L7" s="12"/>
+    </row>
+    <row r="8" ht="21" customHeight="1" spans="1:12">
       <c r="A8" s="9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="12" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
@@ -1352,8 +1429,11 @@
       <c r="G8" s="12"/>
       <c r="H8" s="12"/>
       <c r="I8" s="12"/>
-    </row>
-    <row r="10" spans="1:9">
+      <c r="J8" s="12"/>
+      <c r="K8" s="12"/>
+      <c r="L8" s="12"/>
+    </row>
+    <row r="10" spans="1:12">
       <c r="A10" s="17"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -1363,8 +1443,11 @@
       <c r="G10" s="17"/>
       <c r="H10" s="17"/>
       <c r="I10" s="17"/>
-    </row>
-    <row r="12" spans="1:9">
+      <c r="J10" s="17"/>
+      <c r="K10" s="17"/>
+      <c r="L10" s="17"/>
+    </row>
+    <row r="12" spans="1:12">
       <c r="A12" s="18"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
@@ -1374,8 +1457,11 @@
       <c r="G12" s="18"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18"/>
-    </row>
-    <row r="13" spans="1:9">
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="18"/>
+    </row>
+    <row r="13" spans="1:12">
       <c r="A13" s="18"/>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
@@ -1385,8 +1471,11 @@
       <c r="G13" s="18"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
-    </row>
-    <row r="14" spans="1:9">
+      <c r="J13" s="18"/>
+      <c r="K13" s="18"/>
+      <c r="L13" s="18"/>
+    </row>
+    <row r="14" spans="1:12">
       <c r="A14" s="18"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
@@ -1396,8 +1485,11 @@
       <c r="G14" s="18"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
-    </row>
-    <row r="15" spans="1:9">
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="18"/>
+    </row>
+    <row r="15" spans="1:12">
       <c r="A15" s="18"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
@@ -1407,8 +1499,11 @@
       <c r="G15" s="18"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
-    </row>
-    <row r="16" spans="1:9">
+      <c r="J15" s="18"/>
+      <c r="K15" s="18"/>
+      <c r="L15" s="18"/>
+    </row>
+    <row r="16" spans="1:12">
       <c r="A16" s="18"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
@@ -1418,8 +1513,11 @@
       <c r="G16" s="18"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
-    </row>
-    <row r="17" spans="1:9">
+      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
+      <c r="L16" s="18"/>
+    </row>
+    <row r="17" spans="1:12">
       <c r="A17" s="18"/>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
@@ -1429,8 +1527,11 @@
       <c r="G17" s="18"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
-    </row>
-    <row r="18" spans="1:9">
+      <c r="J17" s="18"/>
+      <c r="K17" s="18"/>
+      <c r="L17" s="18"/>
+    </row>
+    <row r="18" spans="1:12">
       <c r="A18" s="18"/>
       <c r="B18" s="19"/>
       <c r="C18" s="19"/>
@@ -1440,8 +1541,11 @@
       <c r="G18" s="19"/>
       <c r="H18" s="19"/>
       <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="1:9">
+      <c r="J18" s="19"/>
+      <c r="K18" s="19"/>
+      <c r="L18" s="19"/>
+    </row>
+    <row r="19" spans="1:12">
       <c r="A19" s="18"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
@@ -1451,8 +1555,11 @@
       <c r="G19" s="18"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
-    </row>
-    <row r="20" spans="1:9">
+      <c r="J19" s="18"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="18"/>
+    </row>
+    <row r="20" spans="1:12">
       <c r="A20" s="18"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
@@ -1462,8 +1569,11 @@
       <c r="G20" s="18"/>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
-    </row>
-    <row r="21" spans="1:9">
+      <c r="J20" s="18"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="18"/>
+    </row>
+    <row r="21" spans="1:12">
       <c r="A21" s="18"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
@@ -1473,8 +1583,11 @@
       <c r="G21" s="18"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
-    </row>
-    <row r="22" spans="1:9">
+      <c r="J21" s="18"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="18"/>
+    </row>
+    <row r="22" spans="1:12">
       <c r="A22" s="18"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
@@ -1484,8 +1597,11 @@
       <c r="G22" s="18"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
-    </row>
-    <row r="23" spans="1:9">
+      <c r="J22" s="18"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="18"/>
+    </row>
+    <row r="23" spans="1:12">
       <c r="A23" s="18"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
@@ -1495,8 +1611,11 @@
       <c r="G23" s="18"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
-    </row>
-    <row r="24" spans="1:9">
+      <c r="J23" s="18"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="18"/>
+    </row>
+    <row r="24" spans="1:12">
       <c r="A24" s="18"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
@@ -1506,8 +1625,11 @@
       <c r="G24" s="18"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
-    </row>
-    <row r="25" spans="1:9">
+      <c r="J24" s="18"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="18"/>
+    </row>
+    <row r="25" spans="1:12">
       <c r="A25" s="18"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
@@ -1517,8 +1639,11 @@
       <c r="G25" s="18"/>
       <c r="H25" s="18"/>
       <c r="I25" s="18"/>
-    </row>
-    <row r="26" spans="1:9">
+      <c r="J25" s="18"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="18"/>
+    </row>
+    <row r="26" spans="1:12">
       <c r="A26" s="18"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
@@ -1528,8 +1653,11 @@
       <c r="G26" s="18"/>
       <c r="H26" s="18"/>
       <c r="I26" s="18"/>
-    </row>
-    <row r="27" spans="1:9">
+      <c r="J26" s="18"/>
+      <c r="K26" s="18"/>
+      <c r="L26" s="18"/>
+    </row>
+    <row r="27" spans="1:12">
       <c r="A27" s="18"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
@@ -1539,23 +1667,27 @@
       <c r="G27" s="18"/>
       <c r="H27" s="18"/>
       <c r="I27" s="18"/>
+      <c r="J27" s="18"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:M2"/>
+  <mergeCells count="15">
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="N2:P2"/>
     <mergeCell ref="A3:B3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="O3:P3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
-    <mergeCell ref="H4:I4"/>
-    <mergeCell ref="K5:L5"/>
+    <mergeCell ref="K4:L4"/>
+    <mergeCell ref="N5:O5"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:I7"/>
+    <mergeCell ref="K7:L7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:I8"/>
+    <mergeCell ref="C8:L8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter alignWithMargins="0" scaleWithDoc="0"/>
@@ -1655,42 +1787,42 @@
         <v>14</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>15</v>
+        <v>42</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" s="6" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G6" s="6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -1706,34 +1838,34 @@
     </row>
     <row r="8" spans="1:9">
       <c r="A8" s="9" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="10" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E8" s="12" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="9" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="H8" s="12" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="I8" s="12"/>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="9" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="12" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>

--- a/erp-server/erp-server-scm/src/main/resources/excel/purchaseContractExport.xlsx
+++ b/erp-server/erp-server-scm/src/main/resources/excel/purchaseContractExport.xlsx
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="46">
   <si>
     <t>进货订单</t>
   </si>
@@ -141,25 +141,31 @@
     <t>{sumQty}</t>
   </si>
   <si>
+    <t>合计未税金额：</t>
+  </si>
+  <si>
+    <t>{sumAmount}</t>
+  </si>
+  <si>
+    <t>合计含税金额：</t>
+  </si>
+  <si>
+    <t>{sumTaxAmount}</t>
+  </si>
+  <si>
+    <t>采购主管：</t>
+  </si>
+  <si>
+    <t>{approveUserName}</t>
+  </si>
+  <si>
+    <t>单价</t>
+  </si>
+  <si>
+    <t>金额</t>
+  </si>
+  <si>
     <t>合计金额：</t>
-  </si>
-  <si>
-    <t>{sumAmount}</t>
-  </si>
-  <si>
-    <t>{sumTaxAmount}</t>
-  </si>
-  <si>
-    <t>采购主管：</t>
-  </si>
-  <si>
-    <t>{approveUserName}</t>
-  </si>
-  <si>
-    <t>单价</t>
-  </si>
-  <si>
-    <t>金额</t>
   </si>
 </sst>
 </file>
@@ -200,13 +206,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color indexed="8"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -345,6 +344,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -668,152 +674,152 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -878,12 +884,6 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1208,18 +1208,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr defaultColWidth="10.2857142857143" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="7.42857142857143" style="14" customWidth="1"/>
     <col min="2" max="2" width="6.85714285714286" style="14" customWidth="1"/>
-    <col min="3" max="3" width="16.7142857142857" style="14" customWidth="1"/>
-    <col min="4" max="4" width="19.2857142857143" style="14" customWidth="1"/>
-    <col min="5" max="5" width="8.00952380952381" style="14"/>
-    <col min="6" max="8" width="10.4285714285714" style="14" customWidth="1"/>
-    <col min="9" max="10" width="11.1428571428571" style="14" customWidth="1"/>
+    <col min="3" max="3" width="15.1428571428571" style="14" customWidth="1"/>
+    <col min="4" max="4" width="13.2857142857143" style="14" customWidth="1"/>
+    <col min="5" max="6" width="6.85714285714286" style="14" customWidth="1"/>
+    <col min="7" max="7" width="12.7142857142857" style="14" customWidth="1"/>
+    <col min="8" max="8" width="10.4285714285714" style="14" customWidth="1"/>
+    <col min="9" max="9" width="11.1428571428571" style="14" customWidth="1"/>
+    <col min="10" max="10" width="12.8571428571429" style="14" customWidth="1"/>
     <col min="11" max="11" width="12.5714285714286" style="14" customWidth="1"/>
-    <col min="12" max="12" width="16.8571428571429" style="14" customWidth="1"/>
+    <col min="12" max="12" width="12.7142857142857" style="14" customWidth="1"/>
     <col min="13" max="16384" width="10.2857142857143" style="14"/>
   </cols>
   <sheetData>
@@ -1237,7 +1239,7 @@
       <c r="K1" s="15"/>
       <c r="L1" s="15"/>
     </row>
-    <row r="2" ht="23.4" customHeight="1" spans="1:16">
+    <row r="2" ht="23.4" customHeight="1" spans="1:12">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -1252,11 +1254,8 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
-      <c r="N2" s="20"/>
-      <c r="O2" s="20"/>
-      <c r="P2" s="20"/>
-    </row>
-    <row r="3" ht="22.65" customHeight="1" spans="1:16">
+    </row>
+    <row r="3" ht="22.65" customHeight="1" spans="1:12">
       <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
@@ -1281,11 +1280,8 @@
         <v>6</v>
       </c>
       <c r="L3" s="4"/>
-      <c r="N3" s="21"/>
-      <c r="O3" s="20"/>
-      <c r="P3" s="21"/>
-    </row>
-    <row r="4" ht="20.4" customHeight="1" spans="1:16">
+    </row>
+    <row r="4" ht="20.4" customHeight="1" spans="1:12">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -1302,11 +1298,8 @@
       <c r="J4" s="5"/>
       <c r="K4" s="5"/>
       <c r="L4" s="5"/>
-      <c r="N4" s="21"/>
-      <c r="O4" s="21"/>
-      <c r="P4" s="21"/>
-    </row>
-    <row r="5" s="13" customFormat="1" ht="22" customHeight="1" spans="1:16">
+    </row>
+    <row r="5" s="13" customFormat="1" ht="22" customHeight="1" spans="1:12">
       <c r="A5" s="16" t="s">
         <v>9</v>
       </c>
@@ -1343,9 +1336,6 @@
       <c r="L5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="21"/>
     </row>
     <row r="6" ht="19" customHeight="1" spans="1:12">
       <c r="A6" s="16" t="s">
@@ -1354,7 +1344,7 @@
       <c r="B6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="6" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="7" t="s">
@@ -1408,20 +1398,20 @@
       </c>
       <c r="I7" s="12"/>
       <c r="J7" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="K7" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L7" s="12"/>
     </row>
     <row r="8" ht="21" customHeight="1" spans="1:12">
       <c r="A8" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B8" s="9"/>
       <c r="C8" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D8" s="12"/>
       <c r="E8" s="12"/>
@@ -1672,16 +1662,13 @@
       <c r="L27" s="18"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="12">
     <mergeCell ref="A2:L2"/>
-    <mergeCell ref="N2:P2"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="K3:L3"/>
-    <mergeCell ref="O3:P3"/>
     <mergeCell ref="A4:B4"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="K4:L4"/>
-    <mergeCell ref="N5:O5"/>
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E7:F7"/>
     <mergeCell ref="H7:I7"/>
@@ -1690,6 +1677,7 @@
     <mergeCell ref="C8:L8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="landscape"/>
   <headerFooter alignWithMargins="0" scaleWithDoc="0"/>
 </worksheet>
 </file>
@@ -1787,10 +1775,10 @@
         <v>14</v>
       </c>
       <c r="G5" s="6" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="H5" s="6" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="I5" s="6" t="s">
         <v>20</v>
@@ -1852,7 +1840,7 @@
       </c>
       <c r="F8" s="12"/>
       <c r="G8" s="9" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H8" s="12" t="s">
         <v>38</v>
@@ -1861,11 +1849,11 @@
     </row>
     <row r="9" spans="1:9">
       <c r="A9" s="9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B9" s="9"/>
       <c r="C9" s="12" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D9" s="12"/>
       <c r="E9" s="12"/>
